--- a/documentation/LIKELIHOODS.xlsx
+++ b/documentation/LIKELIHOODS.xlsx
@@ -8,14 +8,14 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/melissaschnure/Library/CloudStorage/Dropbox/Documents_local/Hopkins/SOM_Job/3_Aging_multimorbidity/gmha/documentation/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EC26A042-6435-1D4F-B6A7-8300751E54EE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7D152C34-DFC7-3346-A3E3-D88879218969}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="7300" yWindow="1140" windowWidth="27760" windowHeight="18680" xr2:uid="{4DDDF168-95C4-EA40-8EDC-FC9C3BFB2E1F}"/>
+    <workbookView xWindow="4240" yWindow="1040" windowWidth="27580" windowHeight="17960" xr2:uid="{4DDDF168-95C4-EA40-8EDC-FC9C3BFB2E1F}"/>
   </bookViews>
   <sheets>
     <sheet name="likelihoods" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="181029"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="80" uniqueCount="56">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="80" uniqueCount="57">
   <si>
     <t>Component</t>
   </si>
@@ -210,6 +210,30 @@
   </si>
   <si>
     <t>Years available</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">- Total
+- Age: 0-14, 10-19, 15-24, 15-49, 50+
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow (Body)"/>
+      </rPr>
+      <t>- Age*sex: 15+ male, 15+ female</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">1/256† </t>
+  </si>
+  <si>
+    <t>Source</t>
+  </si>
+  <si>
+    <t>1980-2040 - UPDATED 5/26</t>
   </si>
   <si>
     <r>
@@ -234,30 +258,13 @@
       <t xml:space="preserve">
 2010-2017, 1x weight
 2018 and after, 4x weight
-France: all pre-1995 points removed</t>
+2030-2040 (Population data only): 1x weight</t>
     </r>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">- Total
-- Age: 0-14, 10-19, 15-24, 15-49, 50+
-</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow (Body)"/>
-      </rPr>
-      <t>- Age*sex: 15+ male, 15+ female</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">1/256† </t>
   </si>
   <si>
     <r>
       <t xml:space="preserve">Total: 1/1000‡
+6/2 trying out total weight = 1/100
 </t>
     </r>
     <r>
@@ -268,9 +275,6 @@
       </rPr>
       <t>Weight by age: 80+ age = 0.25x weight</t>
     </r>
-  </si>
-  <si>
-    <t>Source</t>
   </si>
 </sst>
 </file>
@@ -310,12 +314,18 @@
       <name val="Aptos Narrow (Body)"/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -330,7 +340,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -342,6 +352,9 @@
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
   </cellXfs>
@@ -706,7 +719,7 @@
         <v>3</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="D2" s="2" t="s">
         <v>40</v>
@@ -724,7 +737,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="3" spans="1:8" ht="119" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:8" ht="102" x14ac:dyDescent="0.2">
       <c r="A3" s="3" t="s">
         <v>30</v>
       </c>
@@ -734,7 +747,7 @@
       <c r="E3" s="2"/>
       <c r="F3" s="2"/>
       <c r="G3" s="3" t="s">
-        <v>51</v>
+        <v>55</v>
       </c>
       <c r="H3" s="2"/>
     </row>
@@ -801,7 +814,7 @@
         <v>42</v>
       </c>
       <c r="D6" s="4" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="E6" s="1" t="s">
         <v>41</v>
@@ -810,7 +823,7 @@
         <v>10</v>
       </c>
       <c r="G6" s="1" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="H6" s="1" t="s">
         <v>25</v>
@@ -907,8 +920,8 @@
       <c r="D10" s="4" t="s">
         <v>47</v>
       </c>
-      <c r="E10" s="1" t="s">
-        <v>48</v>
+      <c r="E10" s="5" t="s">
+        <v>54</v>
       </c>
       <c r="F10" s="1" t="s">
         <v>21</v>
@@ -920,7 +933,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="11" spans="1:8" ht="51" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:8" ht="85" x14ac:dyDescent="0.2">
       <c r="A11" s="1" t="s">
         <v>31</v>
       </c>
@@ -939,8 +952,8 @@
       <c r="F11" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="G11" s="1" t="s">
-        <v>54</v>
+      <c r="G11" s="5" t="s">
+        <v>56</v>
       </c>
       <c r="H11" s="1" t="s">
         <v>23</v>
